--- a/task-reviews/tables/task_tables_relation_row_compare_label/task_tables_relation_row_compare_label.xlsx
+++ b/task-reviews/tables/task_tables_relation_row_compare_label/task_tables_relation_row_compare_label.xlsx
@@ -3029,7 +3029,263 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Use the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Find which of the two specified rows has the requested value relation in the named column. Compare the Gain entries for rows Demb and Ora. Which row has the higher value?
+          <t>The image shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Use the table values to decide which named row wins the comparison. Look at the Rate column for rows Osmo and Phio. Which row is larger?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
+Answer format: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Ava"}</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Use the table values to decide which named row wins the comparison. Look at the Rate column for rows Osmo and Phio. Which row is larger?
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"answer":"Ava"}</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[587.04, 428.4, 737.52, 481.6], [587.04, 215.6, 737.52, 268.8]], "answer": "Phio"}</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>[[587.04, 428.4, 737.52, 481.6], [587.04, 215.6, 737.52, 268.8]]</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>62414010068278</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/images/higher_of_two_rows/0018.png</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/data/higher_of_two_rows/0018.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="196.5" customHeight="1">
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_relation_row_compare_label</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>higher_of_two_rows</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Work from the styled table shown in the image: a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Answer this question. Which row, Ado or Horn, has the greater value in the Rank column?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
+Answer field: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Ava"}</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Work from the styled table shown in the image: a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Answer this question. Which row, Ado or Horn, has the greater value in the Rank column?
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"answer":"Ava"}</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[587.04, 162.4, 737.52, 215.6], [587.04, 375.2, 737.52, 428.4]], "answer": "Horn"}</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>[[587.04, 162.4, 737.52, 215.6], [587.04, 375.2, 737.52, 428.4]]</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>136338964588108</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/images/higher_of_two_rows/0023.png</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/data/higher_of_two_rows/0023.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="196.5" customHeight="1">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_relation_row_compare_label</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>higher_of_two_rows</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Answer this question. Between rows Oler and Elsy, which has the higher value in the Rank column?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
+Answer format: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Ava"}</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Answer this question. Between rows Oler and Elsy, which has the higher value in the Rank column?
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"answer":"Ava"}</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[436.56, 455.0, 587.04, 521.5], [436.56, 322.0, 587.04, 388.5]], "answer": "Oler"}</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>[[436.56, 455.0, 587.04, 521.5], [436.56, 322.0, 587.04, 388.5]]</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>647294525733918</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/images/higher_of_two_rows/0003.png</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/data/higher_of_two_rows/0003.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="196.5" customHeight="1">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_relation_row_compare_label</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>higher_of_two_rows</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Use the table values to decide which named row wins the comparison. In the Rate column, which row is larger: Ngo or Diaz?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
+Answer field: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Ava"}</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Use the table values to decide which named row wins the comparison. In the Rate column, which row is larger: Ngo or Diaz?
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"answer":"Ava"}</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[286.08, 255.5, 406.464, 322.0], [286.08, 322.0, 406.464, 388.5]], "answer": "Diaz"}</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>[[286.08, 255.5, 406.464, 322.0], [286.08, 322.0, 406.464, 388.5]]</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>666970004914745</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/images/higher_of_two_rows/0006.png</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/data/higher_of_two_rows/0006.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="196.5" customHeight="1">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_relation_row_compare_label</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>higher_of_two_rows</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Work from the styled table shown in the image: a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Find which of the two specified rows has the requested value relation in the named column. Between rows Hege and Iow, which has the higher value in the Dist column?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
 Answer: set "answer" to the row label with the requested higher or lower value.
@@ -3037,63 +3293,319 @@
 {"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Ava"}</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Find which of the two specified rows has the requested value relation in the named column. Compare the Gain entries for rows Demb and Ora. Which row has the higher value?
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Work from the styled table shown in the image: a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Find which of the two specified rows has the requested value relation in the named column. Between rows Hege and Iow, which has the higher value in the Dist column?
 Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"answer":"Ava"}</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[737.52, 499.333, 888.0, 588.0], [737.52, 410.667, 888.0, 499.333]], "answer": "Hege"}</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>[[737.52, 499.333, 888.0, 588.0], [737.52, 410.667, 888.0, 499.333]]</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>1117109426925871</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/images/higher_of_two_rows/0022.png</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/data/higher_of_two_rows/0022.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="196.5" customHeight="1">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_relation_row_compare_label</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>higher_of_two_rows</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Work from the styled table shown in the image: a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Compare the two named rows in the requested numeric column. Between rows Fae and Bodi, which has the higher value in the Rate column?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
+Answer requirement: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Ava"}</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Work from the styled table shown in the image: a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Compare the two named rows in the requested numeric column. Between rows Fae and Bodi, which has the higher value in the Rate column?
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"answer":"Ava"}</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[587.04, 104.364, 737.52, 152.727], [587.04, 491.273, 737.52, 539.636]], "answer": "Fae"}</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>[[587.04, 104.364, 737.52, 152.727], [587.04, 491.273, 737.52, 539.636]]</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>1426486595376763</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/images/higher_of_two_rows/0020.png</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/data/higher_of_two_rows/0020.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="196.5" customHeight="1">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_relation_row_compare_label</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>higher_of_two_rows</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Work from the styled table shown in the image: a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Use the table values to decide which named row wins the comparison. Which row, Jer or Pooh, has the greater value in the Mass column?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
+Answer field: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Ava"}</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Work from the styled table shown in the image: a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Use the table values to decide which named row wins the comparison. Which row, Jer or Pooh, has the greater value in the Mass column?
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"answer":"Ava"}</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[737.52, 144.667, 888.0, 233.333], [737.52, 322.0, 888.0, 410.667]], "answer": "Jer"}</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>[[737.52, 144.667, 888.0, 233.333], [737.52, 322.0, 888.0, 410.667]]</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>1549712293994065</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/images/higher_of_two_rows/0024.png</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/data/higher_of_two_rows/0024.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="196.5" customHeight="1">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_relation_row_compare_label</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>higher_of_two_rows</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Use the table in the image. It shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Find which of the two specified rows has the requested value relation in the named column. Look at the Rank column for rows Eden and Ryle. Which row is larger?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
 Answer rule: set "answer" to the row label with the requested higher or lower value.
 Example JSON:
+{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Ava"}</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Use the table in the image. It shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Find which of the two specified rows has the requested value relation in the named column. Look at the Rank column for rows Eden and Ryle. Which row is larger?
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
 {"answer":"Ava"}</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[286.08, 534.8, 486.72, 588.0], [286.08, 481.6, 486.72, 534.8]], "answer": "Ora"}</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>[[286.08, 534.8, 486.72, 588.0], [286.08, 481.6, 486.72, 534.8]]</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[486.72, 491.273, 687.36, 539.636], [486.72, 104.364, 687.36, 152.727]], "answer": "Eden"}</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>[[486.72, 491.273, 687.36, 539.636], [486.72, 104.364, 687.36, 152.727]]</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K2" t="n">
-        <v>269356002365440</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/images/higher_of_two_rows/0010.png</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/data/higher_of_two_rows/0010.json</t>
+      <c r="K9" t="n">
+        <v>2042120194700638</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/images/higher_of_two_rows/0016.png</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/data/higher_of_two_rows/0016.json</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="196.5" customHeight="1">
-      <c r="C3" s="2" t="inlineStr">
+    <row r="10" ht="196.5" customHeight="1">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>task_tables_relation_row_compare_label</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>higher_of_two_rows</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>You are given a table: a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Use the table values to decide which named row wins the comparison. In the Time column, which row is larger: Hime or Gail?
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Find which of the two specified rows has the requested value relation in the named column. Look at the Dist column for rows Cash and Dena. Which row is larger?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
+Answer requirement: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Ava"}</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Find which of the two specified rows has the requested value relation in the named column. Look at the Dist column for rows Cash and Dena. Which row is larger?
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"answer":"Ava"}</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[647.232, 322.0, 767.616, 388.5], [647.232, 189.0, 767.616, 255.5]], "answer": "Dena"}</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>[[647.232, 322.0, 767.616, 388.5], [647.232, 189.0, 767.616, 255.5]]</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>2171516122361811</v>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/images/higher_of_two_rows/0019.png</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/data/higher_of_two_rows/0019.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="196.5" customHeight="1">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_relation_row_compare_label</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>higher_of_two_rows</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Answer this question. Between rows Con and Doy, which has the higher value in the Gain column?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence requirement: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
 Answer format: set "answer" to the row label with the requested higher or lower value.
@@ -3101,63 +3613,191 @@
 {"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Ava"}</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>You are given a table: a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Use the table values to decide which named row wins the comparison. In the Time column, which row is larger: Hime or Gail?
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Answer this question. Between rows Con and Doy, which has the higher value in the Gain column?
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"answer":"Ava"}</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[486.72, 521.5, 687.36, 588.0], [486.72, 189.0, 687.36, 255.5]], "answer": "Con"}</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>[[486.72, 521.5, 687.36, 588.0], [486.72, 189.0, 687.36, 255.5]]</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>3104716901119160</v>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/images/higher_of_two_rows/0007.png</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/data/higher_of_two_rows/0007.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="196.5" customHeight="1">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_relation_row_compare_label</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>higher_of_two_rows</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Answer this question. Between rows Tina and Wald, which has the higher value in the Dist column?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
+Answer rule: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Ava"}</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Answer this question. Between rows Tina and Wald, which has the higher value in the Dist column?
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"answer":"Ava"}</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[647.232, 144.667, 767.616, 233.333], [647.232, 499.333, 767.616, 588.0]], "answer": "Wald"}</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>[[647.232, 144.667, 767.616, 233.333], [647.232, 499.333, 767.616, 588.0]]</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>3725407971708158</v>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/images/higher_of_two_rows/0002.png</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/data/higher_of_two_rows/0002.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="196.5" customHeight="1">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_relation_row_compare_label</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>higher_of_two_rows</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Look at the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Compare the two named rows in the requested numeric column. Which row, Sams or Saks, has the greater value in the Temp column?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
+Answer field: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Ava"}</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Look at the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Compare the two named rows in the requested numeric column. Which row, Sams or Saks, has the greater value in the Temp column?
 Return a valid JSON object with key "answer".
 Answer format: set "answer" to the row label with the requested higher or lower value.
 Example JSON:
 {"answer":"Ava"}</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[647.232, 189.0, 767.616, 255.5], [647.232, 455.0, 767.616, 521.5]], "answer": "Gail"}</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>[[647.232, 189.0, 767.616, 255.5], [647.232, 455.0, 767.616, 521.5]]</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[286.08, 410.667, 486.72, 469.778], [286.08, 351.556, 486.72, 410.667]], "answer": "Sams"}</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>[[286.08, 410.667, 486.72, 469.778], [286.08, 351.556, 486.72, 410.667]]</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K3" t="n">
-        <v>1340029919381449</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/images/higher_of_two_rows/0000.png</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/data/higher_of_two_rows/0000.json</t>
+      <c r="K13" t="n">
+        <v>3999241974391937</v>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/images/higher_of_two_rows/0014.png</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/data/higher_of_two_rows/0014.json</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="196.5" customHeight="1">
-      <c r="C4" s="2" t="inlineStr">
+    <row r="14" ht="196.5" customHeight="1">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>task_tables_relation_row_compare_label</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>higher_of_two_rows</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Work from the styled table shown in the image: a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Read the table and report which named row satisfies the requested comparison. Look at the Rank column for rows Walt and Ethe. Which row is larger?
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Answer this question. Between rows Tam and Happ, which has the higher value in the Rate column?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
 Answer: set "answer" to the row label with the requested higher or lower value.
@@ -3165,63 +3805,319 @@
 {"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Ava"}</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Work from the styled table shown in the image: a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Read the table and report which named row satisfies the requested comparison. Look at the Rank column for rows Walt and Ethe. Which row is larger?
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Answer this question. Between rows Tam and Happ, which has the higher value in the Rate column?
 Return a valid JSON object with key "answer".
+Answer: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"answer":"Ava"}</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[286.08, 132.0, 436.56, 208.0], [286.08, 208.0, 436.56, 284.0]], "answer": "Tam"}</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>[[286.08, 132.0, 436.56, 208.0], [286.08, 208.0, 436.56, 284.0]]</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>4481970884084731</v>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/images/higher_of_two_rows/0004.png</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/data/higher_of_two_rows/0004.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="196.5" customHeight="1">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_relation_row_compare_label</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>higher_of_two_rows</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Read the table and report which named row satisfies the requested comparison. Look at the Time column for rows Cath and Betz. Which row is larger?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
 Answer field: set "answer" to the row label with the requested higher or lower value.
 Example JSON:
+{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Ava"}</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Read the table and report which named row satisfies the requested comparison. Look at the Time column for rows Cath and Betz. Which row is larger?
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
 {"answer":"Ava"}</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[647.232, 394.545, 767.616, 442.909], [647.232, 346.182, 767.616, 394.545]], "answer": "Walt"}</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>[[647.232, 394.545, 767.616, 442.909], [647.232, 346.182, 767.616, 394.545]]</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[526.848, 455.0, 647.232, 521.5], [526.848, 322.0, 647.232, 388.5]], "answer": "Betz"}</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>[[526.848, 455.0, 647.232, 521.5], [526.848, 322.0, 647.232, 388.5]]</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K4" t="n">
-        <v>1660639147782970</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/images/higher_of_two_rows/0024.png</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/data/higher_of_two_rows/0024.json</t>
+      <c r="K15" t="n">
+        <v>4718530992315494</v>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/images/higher_of_two_rows/0013.png</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/data/higher_of_two_rows/0013.json</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="196.5" customHeight="1">
-      <c r="C5" s="2" t="inlineStr">
+    <row r="16" ht="196.5" customHeight="1">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>task_tables_relation_row_compare_label</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>higher_of_two_rows</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Find which of the two specified rows has the requested value relation in the named column. Look at the Score column for rows Adi and Isla. Which row is larger?
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Look at the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Read the table and report which named row satisfies the requested comparison. In the Age column, which row is larger: Radu or Flem?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
+Answer requirement: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Ava"}</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Look at the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Read the table and report which named row satisfies the requested comparison. In the Age column, which row is larger: Radu or Flem?
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"answer":"Ava"}</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[526.848, 534.8, 647.232, 588.0], [526.848, 481.6, 647.232, 534.8]], "answer": "Flem"}</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>[[526.848, 534.8, 647.232, 588.0], [526.848, 481.6, 647.232, 534.8]]</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>5276958994175210</v>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/images/higher_of_two_rows/0021.png</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/data/higher_of_two_rows/0021.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="196.5" customHeight="1">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_relation_row_compare_label</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>higher_of_two_rows</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Look at the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Answer this question. Look at the Cost column for rows Saks and Fax. Which row is larger?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
+Answer field: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Ava"}</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Look at the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Answer this question. Look at the Cost column for rows Saks and Fax. Which row is larger?
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"answer":"Ava"}</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[286.08, 410.667, 436.56, 499.333], [286.08, 322.0, 436.56, 410.667]], "answer": "Fax"}</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>[[286.08, 410.667, 436.56, 499.333], [286.08, 322.0, 436.56, 410.667]]</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>5651035252480628</v>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/images/higher_of_two_rows/0017.png</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/data/higher_of_two_rows/0017.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="196.5" customHeight="1">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_relation_row_compare_label</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>higher_of_two_rows</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Find which of the two specified rows has the requested value relation in the named column. In the Dist column, which row is larger: Ora or Tobi?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
+Answer field: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Ava"}</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Find which of the two specified rows has the requested value relation in the named column. In the Dist column, which row is larger: Ora or Tobi?
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"answer":"Ava"}</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[486.72, 410.667, 687.36, 499.333], [486.72, 499.333, 687.36, 588.0]], "answer": "Tobi"}</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>[[486.72, 410.667, 687.36, 499.333], [486.72, 499.333, 687.36, 588.0]]</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>6548686095711062</v>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/images/higher_of_two_rows/0005.png</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/data/higher_of_two_rows/0005.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="196.5" customHeight="1">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_relation_row_compare_label</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>higher_of_two_rows</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Look at the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Compare the two named rows in the requested numeric column. Compare the Rate entries for rows Ames and Neil. Which row has the higher value?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence rule: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
 Answer rule: set "answer" to the row label with the requested higher or lower value.
@@ -3229,63 +4125,63 @@
 {"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Ava"}</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Find which of the two specified rows has the requested value relation in the named column. Look at the Score column for rows Adi and Isla. Which row is larger?
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Look at the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Compare the two named rows in the requested numeric column. Compare the Rate entries for rows Ames and Neil. Which row has the higher value?
 Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the row label with the requested higher or lower value.
+Answer field: set "answer" to the row label with the requested higher or lower value.
 Example JSON:
 {"answer":"Ava"}</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[436.56, 174.222, 587.04, 233.333], [436.56, 469.778, 587.04, 528.889]], "answer": "Isla"}</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>[[436.56, 174.222, 587.04, 233.333], [436.56, 469.778, 587.04, 528.889]]</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[286.08, 115.111, 486.72, 174.222], [286.08, 233.333, 486.72, 292.444]], "answer": "Ames"}</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>[[286.08, 115.111, 486.72, 174.222], [286.08, 233.333, 486.72, 292.444]]</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K5" t="n">
-        <v>1831775285583634</v>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/images/higher_of_two_rows/0023.png</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/data/higher_of_two_rows/0023.json</t>
+      <c r="K19" t="n">
+        <v>6728997312102880</v>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/images/higher_of_two_rows/0008.png</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/data/higher_of_two_rows/0008.json</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="196.5" customHeight="1">
-      <c r="C6" s="2" t="inlineStr">
+    <row r="20" ht="196.5" customHeight="1">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>task_tables_relation_row_compare_label</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>higher_of_two_rows</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Find which of the two specified rows has the requested value relation in the named column. Look at the Pts column for rows Nara and Tran. Which row is larger?
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Look at the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Compare the two named rows in the requested numeric column. In the Age column, which row is larger: Wait or Pani?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence format: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
 Answer requirement: set "answer" to the row label with the requested higher or lower value.
@@ -3293,575 +4189,127 @@
 {"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Ava"}</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Find which of the two specified rows has the requested value relation in the named column. Look at the Pts column for rows Nara and Tran. Which row is larger?
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Look at the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Compare the two named rows in the requested numeric column. In the Age column, which row is larger: Wait or Pani?
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"answer":"Ava"}</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[647.232, 410.667, 767.616, 499.333], [647.232, 144.667, 767.616, 233.333]], "answer": "Wait"}</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>[[647.232, 410.667, 767.616, 499.333], [647.232, 144.667, 767.616, 233.333]]</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>6898652781342913</v>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/images/higher_of_two_rows/0000.png</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/data/higher_of_two_rows/0000.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="196.5" customHeight="1">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_relation_row_compare_label</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>higher_of_two_rows</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Use the table in the image. It shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Find which of the two specified rows has the requested value relation in the named column. In the Wins column, which row is larger: Uni or Rew?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
+Answer requirement: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Ava"}</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Use the table in the image. It shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Find which of the two specified rows has the requested value relation in the named column. In the Wins column, which row is larger: Uni or Rew?
 Return a valid JSON object with key "answer".
 Answer: set "answer" to the row label with the requested higher or lower value.
 Example JSON:
 {"answer":"Ava"}</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[737.52, 410.667, 888.0, 499.333], [737.52, 144.667, 888.0, 233.333]], "answer": "Nara"}</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>[[737.52, 410.667, 888.0, 499.333], [737.52, 144.667, 888.0, 233.333]]</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[526.848, 469.778, 647.232, 528.889], [526.848, 174.222, 647.232, 233.333]], "answer": "Rew"}</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>[[526.848, 469.778, 647.232, 528.889], [526.848, 174.222, 647.232, 233.333]]</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K6" t="n">
-        <v>1926563012980744</v>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/images/higher_of_two_rows/0019.png</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/data/higher_of_two_rows/0019.json</t>
+      <c r="K21" t="n">
+        <v>7270251792816341</v>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/images/higher_of_two_rows/0015.png</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/data/higher_of_two_rows/0015.json</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="196.5" customHeight="1">
-      <c r="C7" s="2" t="inlineStr">
+    <row r="22" ht="196.5" customHeight="1">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>task_tables_relation_row_compare_label</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>higher_of_two_rows</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Compare the two named rows in the requested numeric column. Compare the Pts entries for rows Ly and Froh. Which row has the higher value?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
-Answer rule: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Ava"}</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Compare the two named rows in the requested numeric column. Compare the Pts entries for rows Ly and Froh. Which row has the higher value?
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"answer":"Ava"}</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[406.464, 346.182, 526.848, 394.545], [406.464, 442.909, 526.848, 491.273]], "answer": "Ly"}</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>[[406.464, 346.182, 526.848, 394.545], [406.464, 442.909, 526.848, 491.273]]</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>1942170967630954</v>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/images/higher_of_two_rows/0022.png</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/data/higher_of_two_rows/0022.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="196.5" customHeight="1">
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>higher_of_two_rows</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>You are given a table: a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Use the table values to decide which named row wins the comparison. In the Gain column, which row is larger: Vi or Aryn?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
-Answer format: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Ava"}</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>You are given a table: a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Use the table values to decide which named row wins the comparison. In the Gain column, which row is larger: Vi or Aryn?
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"answer":"Ava"}</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[687.36, 144.667, 888.0, 233.333], [687.36, 233.333, 888.0, 322.0]], "answer": "Aryn"}</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>[[687.36, 144.667, 888.0, 233.333], [687.36, 233.333, 888.0, 322.0]]</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>2156105016797569</v>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/images/higher_of_two_rows/0017.png</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/data/higher_of_two_rows/0017.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="196.5" customHeight="1">
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>higher_of_two_rows</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>You are given a table: a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Answer this question. Look at the Rank column for rows Tony and Hoag. Which row is larger?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
-Answer format: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Ava"}</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>You are given a table: a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Answer this question. Look at the Rank column for rows Tony and Hoag. Which row is larger?
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"answer":"Ava"}</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[286.08, 268.8, 486.72, 322.0], [286.08, 215.6, 486.72, 268.8]], "answer": "Tony"}</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>[[286.08, 268.8, 486.72, 322.0], [286.08, 215.6, 486.72, 268.8]]</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>2476868559823740</v>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/images/higher_of_two_rows/0015.png</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/data/higher_of_two_rows/0015.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="196.5" customHeight="1">
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>higher_of_two_rows</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Work from the styled table shown in the image: a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Read the table and report which named row satisfies the requested comparison. Between rows Orsa and Tait, which has the higher value in the Rate column?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
-Answer format: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Ava"}</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Work from the styled table shown in the image: a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Read the table and report which named row satisfies the requested comparison. Between rows Orsa and Tait, which has the higher value in the Rate column?
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"answer":"Ava"}</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[286.08, 442.909, 406.464, 491.273], [286.08, 394.545, 406.464, 442.909]], "answer": "Orsa"}</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>[[286.08, 442.909, 406.464, 491.273], [286.08, 394.545, 406.464, 442.909]]</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>2483508579638834</v>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/images/higher_of_two_rows/0006.png</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/data/higher_of_two_rows/0006.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="196.5" customHeight="1">
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>higher_of_two_rows</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Compare the two named rows in the requested numeric column. In the Gain column, which row is larger: Paco or Inez?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
-Answer format: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Ava"}</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Compare the two named rows in the requested numeric column. In the Gain column, which row is larger: Paco or Inez?
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"answer":"Ava"}</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[486.72, 201.091, 687.36, 249.455], [486.72, 104.364, 687.36, 152.727]], "answer": "Inez"}</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>[[486.72, 201.091, 687.36, 249.455], [486.72, 104.364, 687.36, 152.727]]</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>2559429588734586</v>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/images/higher_of_two_rows/0011.png</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/data/higher_of_two_rows/0011.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="196.5" customHeight="1">
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>higher_of_two_rows</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Find which of the two specified rows has the requested value relation in the named column. Look at the Gain column for rows Soo and Hako. Which row is larger?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
-Answer field: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Ava"}</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Find which of the two specified rows has the requested value relation in the named column. Look at the Gain column for rows Soo and Hako. Which row is larger?
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"answer":"Ava"}</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[486.72, 233.333, 687.36, 322.0], [486.72, 499.333, 687.36, 588.0]], "answer": "Hako"}</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>[[486.72, 233.333, 687.36, 322.0], [486.72, 499.333, 687.36, 588.0]]</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>2801296396992692</v>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/images/higher_of_two_rows/0018.png</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/data/higher_of_two_rows/0018.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="196.5" customHeight="1">
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>higher_of_two_rows</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>You are given a table: a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Compare the two named rows in the requested numeric column. Compare the Rate entries for rows York and Fia. Which row has the higher value?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
-Answer field: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Ava"}</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>You are given a table: a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Compare the two named rows in the requested numeric column. Compare the Rate entries for rows York and Fia. Which row has the higher value?
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"answer":"Ava"}</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[526.848, 436.0, 647.232, 512.0], [526.848, 284.0, 647.232, 360.0]], "answer": "York"}</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>[[526.848, 436.0, 647.232, 512.0], [526.848, 284.0, 647.232, 360.0]]</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>3881664308376647</v>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/images/higher_of_two_rows/0001.png</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/data/higher_of_two_rows/0001.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="196.5" customHeight="1">
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>higher_of_two_rows</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Find which of the two specified rows has the requested value relation in the named column. Compare the Rank entries for rows Bron and Papp. Which row has the higher value?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
-Answer rule: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Ava"}</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Find which of the two specified rows has the requested value relation in the named column. Compare the Rank entries for rows Bron and Papp. Which row has the higher value?
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"answer":"Ava"}</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[687.36, 375.2, 888.0, 428.4], [687.36, 322.0, 888.0, 375.2]], "answer": "Bron"}</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>[[687.36, 375.2, 888.0, 428.4], [687.36, 322.0, 888.0, 375.2]]</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>5158537556079896</v>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/images/higher_of_two_rows/0008.png</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/data/higher_of_two_rows/0008.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="196.5" customHeight="1">
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>higher_of_two_rows</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Read the table and report which named row satisfies the requested comparison. Look at the Cost column for rows Borg and Jan. Which row is larger?
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Use the table values to decide which named row wins the comparison. Between rows Nett and Bran, which has the higher value in the Cost column?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
 Answer: set "answer" to the row label with the requested higher or lower value.
@@ -3869,127 +4317,63 @@
 {"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Ava"}</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Read the table and report which named row satisfies the requested comparison. Look at the Cost column for rows Borg and Jan. Which row is larger?
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"answer":"Ava"}</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[406.464, 481.6, 526.848, 534.8], [406.464, 375.2, 526.848, 428.4]], "answer": "Borg"}</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>[[406.464, 481.6, 526.848, 534.8], [406.464, 375.2, 526.848, 428.4]]</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>5275538138728087</v>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/images/higher_of_two_rows/0021.png</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/data/higher_of_two_rows/0021.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="196.5" customHeight="1">
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>higher_of_two_rows</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Compare the two named rows in the requested numeric column. In the Cost column, which row is larger: Feld or Case?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
-Answer requirement: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Ava"}</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Compare the two named rows in the requested numeric column. In the Cost column, which row is larger: Feld or Case?
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Use the table values to decide which named row wins the comparison. Between rows Nett and Bran, which has the higher value in the Cost column?
 Return a valid JSON object with key "answer".
 Answer format: set "answer" to the row label with the requested higher or lower value.
 Example JSON:
 {"answer":"Ava"}</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[737.52, 284.0, 888.0, 360.0], [737.52, 208.0, 888.0, 284.0]], "answer": "Feld"}</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>[[737.52, 284.0, 888.0, 360.0], [737.52, 208.0, 888.0, 284.0]]</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[647.232, 132.0, 767.616, 208.0], [647.232, 284.0, 767.616, 360.0]], "answer": "Bran"}</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>[[647.232, 132.0, 767.616, 208.0], [647.232, 284.0, 767.616, 360.0]]</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K16" t="n">
-        <v>5290319268431728</v>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/images/higher_of_two_rows/0016.png</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/data/higher_of_two_rows/0016.json</t>
+      <c r="K22" t="n">
+        <v>8021164251546690</v>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/images/higher_of_two_rows/0012.png</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/data/higher_of_two_rows/0012.json</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="196.5" customHeight="1">
-      <c r="C17" s="2" t="inlineStr">
+    <row r="23" ht="196.5" customHeight="1">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>task_tables_relation_row_compare_label</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>higher_of_two_rows</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>You are given a table: a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Answer this question. Which row, Ri or Leno, has the greater value in the Rate column?
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Answer this question. Between rows Fry and Sou, which has the higher value in the Cost column?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
 Answer: set "answer" to the row label with the requested higher or lower value.
@@ -3997,255 +4381,63 @@
 {"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Ava"}</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>You are given a table: a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Answer this question. Which row, Ri or Leno, has the greater value in the Rate column?
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Answer this question. Between rows Fry and Sou, which has the higher value in the Cost column?
 Return a valid JSON object with key "answer".
-Answer: set "answer" to the row label with the requested higher or lower value.
+Answer requirement: set "answer" to the row label with the requested higher or lower value.
 Example JSON:
 {"answer":"Ava"}</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[767.616, 375.2, 888.0, 428.4], [767.616, 534.8, 888.0, 588.0]], "answer": "Ri"}</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>[[767.616, 375.2, 888.0, 428.4], [767.616, 534.8, 888.0, 588.0]]</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[486.72, 132.0, 687.36, 208.0], [486.72, 208.0, 687.36, 284.0]], "answer": "Fry"}</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>[[486.72, 132.0, 687.36, 208.0], [486.72, 208.0, 687.36, 284.0]]</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K17" t="n">
-        <v>5343965249387504</v>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/images/higher_of_two_rows/0014.png</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/data/higher_of_two_rows/0014.json</t>
+      <c r="K23" t="n">
+        <v>8433210260383693</v>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/images/higher_of_two_rows/0009.png</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/data/higher_of_two_rows/0009.json</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="196.5" customHeight="1">
-      <c r="C18" s="2" t="inlineStr">
+    <row r="24" ht="196.5" customHeight="1">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>task_tables_relation_row_compare_label</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>higher_of_two_rows</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Read the table and report which named row satisfies the requested comparison. Compare the Rate entries for rows Rise and Noah. Which row has the higher value?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
-Answer rule: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Ava"}</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Read the table and report which named row satisfies the requested comparison. Compare the Rate entries for rows Rise and Noah. Which row has the higher value?
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"answer":"Ava"}</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[737.52, 132.0, 888.0, 208.0], [737.52, 436.0, 888.0, 512.0]], "answer": "Noah"}</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>[[737.52, 132.0, 888.0, 208.0], [737.52, 436.0, 888.0, 512.0]]</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>5950524869060389</v>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/images/higher_of_two_rows/0007.png</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/data/higher_of_two_rows/0007.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="196.5" customHeight="1">
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>higher_of_two_rows</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Work from the styled table shown in the image: a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Answer this question. In the Temp column, which row is larger: Crim or Keon?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
-Answer requirement: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Ava"}</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Work from the styled table shown in the image: a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Answer this question. In the Temp column, which row is larger: Crim or Keon?
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"answer":"Ava"}</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[526.848, 346.182, 647.232, 394.545], [526.848, 201.091, 647.232, 249.455]], "answer": "Keon"}</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>[[526.848, 346.182, 647.232, 394.545], [526.848, 201.091, 647.232, 249.455]]</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>6328680240299764</v>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/images/higher_of_two_rows/0004.png</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/data/higher_of_two_rows/0004.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="196.5" customHeight="1">
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>higher_of_two_rows</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Find which of the two specified rows has the requested value relation in the named column. Compare the Dist entries for rows Alf and Nert. Which row has the higher value?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
-Answer requirement: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Ava"}</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Find which of the two specified rows has the requested value relation in the named column. Compare the Dist entries for rows Alf and Nert. Which row has the higher value?
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"answer":"Ava"}</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[486.72, 297.818, 687.36, 346.182], [486.72, 539.636, 687.36, 588.0]], "answer": "Alf"}</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>[[486.72, 297.818, 687.36, 346.182], [486.72, 539.636, 687.36, 588.0]]</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>7071069740036760</v>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/images/higher_of_two_rows/0020.png</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/data/higher_of_two_rows/0020.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="196.5" customHeight="1">
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>higher_of_two_rows</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Read the table and report which named row satisfies the requested comparison. Compare the Score entries for rows Ma and Tyra. Which row has the higher value?
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Answer this question. In the Time column, which row is larger: Ivon or Bigg?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
 Answer: set "answer" to the row label with the requested higher or lower value.
@@ -4253,238 +4445,46 @@
 {"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Ava"}</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Read the table and report which named row satisfies the requested comparison. Compare the Score entries for rows Ma and Tyra. Which row has the higher value?
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Answer this question. In the Time column, which row is larger: Ivon or Bigg?
 Return a valid JSON object with key "answer".
 Answer format: set "answer" to the row label with the requested higher or lower value.
 Example JSON:
 {"answer":"Ava"}</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[526.848, 268.8, 647.232, 322.0], [526.848, 428.4, 647.232, 481.6]], "answer": "Tyra"}</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>[[526.848, 268.8, 647.232, 322.0], [526.848, 428.4, 647.232, 481.6]]</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[587.04, 388.5, 737.52, 455.0], [587.04, 521.5, 737.52, 588.0]], "answer": "Ivon"}</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>[[587.04, 388.5, 737.52, 455.0], [587.04, 521.5, 737.52, 588.0]]</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K21" t="n">
-        <v>7312771295294554</v>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/images/higher_of_two_rows/0003.png</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/data/higher_of_two_rows/0003.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="196.5" customHeight="1">
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>higher_of_two_rows</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Use the table values to decide which named row wins the comparison. Look at the Rank column for rows Zela and Sol. Which row is larger?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
-Answer rule: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Ava"}</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Use the table values to decide which named row wins the comparison. Look at the Rank column for rows Zela and Sol. Which row is larger?
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"answer":"Ava"}</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[526.848, 322.0, 647.232, 388.5], [526.848, 122.5, 647.232, 189.0]], "answer": "Zela"}</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>[[526.848, 322.0, 647.232, 388.5], [526.848, 122.5, 647.232, 189.0]]</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>8074915774578784</v>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/images/higher_of_two_rows/0002.png</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/data/higher_of_two_rows/0002.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="196.5" customHeight="1">
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>higher_of_two_rows</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Use the table values to decide which named row wins the comparison. In the Rate column, which row is larger: Will or Asta?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
-Answer requirement: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Ava"}</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Use the table values to decide which named row wins the comparison. In the Rate column, which row is larger: Will or Asta?
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"answer":"Ava"}</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[526.848, 144.667, 647.232, 233.333], [526.848, 410.667, 647.232, 499.333]], "answer": "Will"}</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>[[526.848, 144.667, 647.232, 233.333], [526.848, 410.667, 647.232, 499.333]]</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K23" t="n">
-        <v>8260398825576674</v>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/images/higher_of_two_rows/0009.png</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/data/higher_of_two_rows/0009.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="196.5" customHeight="1">
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>higher_of_two_rows</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Find which of the two specified rows has the requested value relation in the named column. Compare the Pts entries for rows Emad and Huai. Which row has the higher value?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
-Answer field: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Ava"}</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Find which of the two specified rows has the requested value relation in the named column. Compare the Pts entries for rows Emad and Huai. Which row has the higher value?
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"answer":"Ava"}</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[687.36, 528.889, 888.0, 588.0], [687.36, 351.556, 888.0, 410.667]], "answer": "Emad"}</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>[[687.36, 528.889, 888.0, 588.0], [687.36, 351.556, 888.0, 410.667]]</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
       <c r="K24" t="n">
-        <v>8420868581827948</v>
+        <v>8448502167063150</v>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>task_tables_relation_row_compare_label/images/higher_of_two_rows/0005.png</t>
+          <t>tables/task_tables_relation_row_compare_label/images/higher_of_two_rows/0010.png</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>task_tables_relation_row_compare_label/data/higher_of_two_rows/0005.json</t>
+          <t>tables/task_tables_relation_row_compare_label/data/higher_of_two_rows/0010.json</t>
         </is>
       </c>
     </row>
@@ -4501,17 +4501,17 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Work from the styled table shown in the image: a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Find which of the two specified rows has the requested value relation in the named column. Which row, Tien or Cos, has the greater value in the Wins column?
+          <t>You are given a table: a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Find which of the two specified rows has the requested value relation in the named column. In the Score column, which row is larger: Katz or Tips?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
-Answer field: set "answer" to the row label with the requested higher or lower value.
+Evidence: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
+Answer: set "answer" to the row label with the requested higher or lower value.
 Example JSON:
 {"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Ava"}</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Work from the styled table shown in the image: a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Find which of the two specified rows has the requested value relation in the named column. Which row, Tien or Cos, has the greater value in the Wins column?
+          <t>You are given a table: a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Find which of the two specified rows has the requested value relation in the named column. In the Score column, which row is larger: Katz or Tips?
 Return a valid JSON object with key "answer".
 Answer requirement: set "answer" to the row label with the requested higher or lower value.
 Example JSON:
@@ -4520,12 +4520,12 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": [[406.464, 499.333, 526.848, 588.0], [406.464, 144.667, 526.848, 233.333]], "answer": "Cos"}</t>
+          <t>{"evidence": [[587.04, 132.0, 737.52, 208.0], [587.04, 208.0, 737.52, 284.0]], "answer": "Katz"}</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>[[406.464, 499.333, 526.848, 588.0], [406.464, 144.667, 526.848, 233.333]]</t>
+          <t>[[587.04, 132.0, 737.52, 208.0], [587.04, 208.0, 737.52, 284.0]]</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -4539,16 +4539,16 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>8428717651449026</v>
+        <v>8928950288679308</v>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>task_tables_relation_row_compare_label/images/higher_of_two_rows/0013.png</t>
+          <t>tables/task_tables_relation_row_compare_label/images/higher_of_two_rows/0001.png</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>task_tables_relation_row_compare_label/data/higher_of_two_rows/0013.json</t>
+          <t>tables/task_tables_relation_row_compare_label/data/higher_of_two_rows/0001.json</t>
         </is>
       </c>
     </row>
@@ -4565,17 +4565,17 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>The image shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Use the table values to decide which named row wins the comparison. In the Score column, which row is larger: Noni or Kin?
+          <t>Use the table in the image. It shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Compare the two named rows in the requested numeric column. Compare the Temp entries for rows Burn and Rose. Which row has the higher value?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
-Answer rule: set "answer" to the row label with the requested higher or lower value.
+Evidence: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
+Answer: set "answer" to the row label with the requested higher or lower value.
 Example JSON:
 {"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Ava"}</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>The image shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Use the table values to decide which named row wins the comparison. In the Score column, which row is larger: Noni or Kin?
+          <t>Use the table in the image. It shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Compare the two named rows in the requested numeric column. Compare the Temp entries for rows Burn and Rose. Which row has the higher value?
 Return a valid JSON object with key "answer".
 Answer: set "answer" to the row label with the requested higher or lower value.
 Example JSON:
@@ -4584,12 +4584,12 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": [[587.04, 292.444, 737.52, 351.556], [587.04, 528.889, 737.52, 588.0]], "answer": "Kin"}</t>
+          <t>{"evidence": [[286.08, 174.222, 406.464, 233.333], [286.08, 410.667, 406.464, 469.778]], "answer": "Rose"}</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>[[587.04, 292.444, 737.52, 351.556], [587.04, 528.889, 737.52, 588.0]]</t>
+          <t>[[286.08, 174.222, 406.464, 233.333], [286.08, 410.667, 406.464, 469.778]]</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -4603,16 +4603,16 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>8708318713075639</v>
+        <v>8945921286924923</v>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>task_tables_relation_row_compare_label/images/higher_of_two_rows/0012.png</t>
+          <t>tables/task_tables_relation_row_compare_label/images/higher_of_two_rows/0011.png</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>task_tables_relation_row_compare_label/data/higher_of_two_rows/0012.json</t>
+          <t>tables/task_tables_relation_row_compare_label/data/higher_of_two_rows/0011.json</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4726,455 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Work from the styled table shown in the image: a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Find which of the two specified rows has the requested value relation in the named column. Between rows Tory and Uird, which has the lower value in the Rate column?
+          <t>You are given a table: a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Compare the two named rows in the requested numeric column. Look at the Rank column for rows Voss and Horn. Which row is smaller?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
+Answer: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Milo"}</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Compare the two named rows in the requested numeric column. Look at the Rank column for rows Voss and Horn. Which row is smaller?
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"answer":"Milo"}</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[406.464, 469.778, 526.848, 528.889], [406.464, 528.889, 526.848, 588.0]], "answer": "Horn"}</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>[[406.464, 469.778, 526.848, 528.889], [406.464, 528.889, 526.848, 588.0]]</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>66322368431738</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/images/lower_of_two_rows/0022.png</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/data/lower_of_two_rows/0022.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="196.5" customHeight="1">
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_relation_row_compare_label</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>lower_of_two_rows</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Read the table and report which named row satisfies the requested comparison. Compare the Dist entries for rows Iain and Kan. Which row has the lower value?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
+Answer: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Milo"}</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Read the table and report which named row satisfies the requested comparison. Compare the Dist entries for rows Iain and Kan. Which row has the lower value?
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"answer":"Milo"}</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[286.08, 201.091, 436.56, 249.455], [286.08, 249.455, 436.56, 297.818]], "answer": "Iain"}</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>[[286.08, 201.091, 436.56, 249.455], [286.08, 249.455, 436.56, 297.818]]</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>218601359548951</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/images/lower_of_two_rows/0014.png</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/data/lower_of_two_rows/0014.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="196.5" customHeight="1">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_relation_row_compare_label</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>lower_of_two_rows</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Use the table in the image. It shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Answer this question. Compare the Rate entries for rows Asta and Luht. Which row has the lower value?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
+Answer: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Milo"}</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Use the table in the image. It shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Answer this question. Compare the Rate entries for rows Asta and Luht. Which row has the lower value?
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"answer":"Milo"}</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[286.08, 297.818, 486.72, 346.182], [286.08, 201.091, 486.72, 249.455]], "answer": "Luht"}</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>[[286.08, 297.818, 486.72, 346.182], [286.08, 201.091, 486.72, 249.455]]</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>712742159555312</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/images/lower_of_two_rows/0020.png</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/data/lower_of_two_rows/0020.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="196.5" customHeight="1">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_relation_row_compare_label</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>lower_of_two_rows</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Look at the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Find which of the two specified rows has the requested value relation in the named column. Look at the Wins column for rows Dave and Curr. Which row is smaller?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
+Answer field: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Milo"}</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Look at the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Find which of the two specified rows has the requested value relation in the named column. Look at the Wins column for rows Dave and Curr. Which row is smaller?
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"answer":"Milo"}</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[526.848, 109.2, 647.232, 162.4], [526.848, 162.4, 647.232, 215.6]], "answer": "Curr"}</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>[[526.848, 109.2, 647.232, 162.4], [526.848, 162.4, 647.232, 215.6]]</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>732404633065125</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/images/lower_of_two_rows/0002.png</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/data/lower_of_two_rows/0002.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="196.5" customHeight="1">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_relation_row_compare_label</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>lower_of_two_rows</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Work from the styled table shown in the image: a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Answer this question. Between rows Ming and Ot, which has the lower value in the Time column?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
+Answer: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Milo"}</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Work from the styled table shown in the image: a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Answer this question. Between rows Ming and Ot, which has the lower value in the Time column?
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"answer":"Milo"}</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[286.08, 152.727, 486.72, 201.091], [286.08, 249.455, 486.72, 297.818]], "answer": "Ot"}</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>[[286.08, 152.727, 486.72, 201.091], [286.08, 249.455, 486.72, 297.818]]</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>895534850113301</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/images/lower_of_two_rows/0006.png</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/data/lower_of_two_rows/0006.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="196.5" customHeight="1">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_relation_row_compare_label</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>lower_of_two_rows</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Answer this question. Look at the Rate column for rows Veno and Nomi. Which row is smaller?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
+Answer: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Milo"}</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Answer this question. Look at the Rate column for rows Veno and Nomi. Which row is smaller?
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"answer":"Milo"}</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[286.08, 322.0, 406.464, 375.2], [286.08, 375.2, 406.464, 428.4]], "answer": "Veno"}</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>[[286.08, 322.0, 406.464, 375.2], [286.08, 375.2, 406.464, 428.4]]</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>998991653873005</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/images/lower_of_two_rows/0024.png</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/data/lower_of_two_rows/0024.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="196.5" customHeight="1">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_relation_row_compare_label</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>lower_of_two_rows</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Answer this question. Compare the Cost entries for rows Zoes and Burn. Which row has the lower value?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
+Answer requirement: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Milo"}</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Answer this question. Compare the Cost entries for rows Zoes and Burn. Which row has the lower value?
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"answer":"Milo"}</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[587.04, 109.2, 737.52, 162.4], [587.04, 534.8, 737.52, 588.0]], "answer": "Burn"}</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>[[587.04, 109.2, 737.52, 162.4], [587.04, 534.8, 737.52, 588.0]]</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>1342049985426988</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/images/lower_of_two_rows/0011.png</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/data/lower_of_two_rows/0011.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="196.5" customHeight="1">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_relation_row_compare_label</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>lower_of_two_rows</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Use the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Compare the two named rows in the requested numeric column. Between rows Powe and Brey, which has the lower value in the Gain column?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence requirement: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
 Answer format: set "answer" to the row label with the requested higher or lower value.
@@ -4734,63 +5182,191 @@
 {"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Milo"}</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Work from the styled table shown in the image: a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Find which of the two specified rows has the requested value relation in the named column. Between rows Tory and Uird, which has the lower value in the Rate column?
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Use the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Compare the two named rows in the requested numeric column. Between rows Powe and Brey, which has the lower value in the Gain column?
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"answer":"Milo"}</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[286.08, 215.6, 406.464, 268.8], [286.08, 375.2, 406.464, 428.4]], "answer": "Brey"}</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>[[286.08, 215.6, 406.464, 268.8], [286.08, 375.2, 406.464, 428.4]]</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>2103823787124203</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/images/lower_of_two_rows/0016.png</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/data/lower_of_two_rows/0016.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="196.5" customHeight="1">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_relation_row_compare_label</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>lower_of_two_rows</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Use the table values to decide which named row wins the comparison. In the Temp column, which row is smaller: Kilk or Deb?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
+Answer rule: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Milo"}</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Use the table values to decide which named row wins the comparison. In the Temp column, which row is smaller: Kilk or Deb?
 Return a valid JSON object with key "answer".
 Answer requirement: set "answer" to the row label with the requested higher or lower value.
 Example JSON:
 {"answer":"Milo"}</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[286.08, 442.909, 436.56, 491.273], [286.08, 539.636, 436.56, 588.0]], "answer": "Tory"}</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>[[286.08, 442.909, 436.56, 491.273], [286.08, 539.636, 436.56, 588.0]]</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[486.72, 442.909, 687.36, 491.273], [486.72, 394.545, 687.36, 442.909]], "answer": "Kilk"}</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>[[486.72, 442.909, 687.36, 491.273], [486.72, 394.545, 687.36, 442.909]]</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K2" t="n">
-        <v>137230575694384</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/images/lower_of_two_rows/0013.png</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/data/lower_of_two_rows/0013.json</t>
+      <c r="K10" t="n">
+        <v>2120163472167873</v>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/images/lower_of_two_rows/0019.png</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/data/lower_of_two_rows/0019.json</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="196.5" customHeight="1">
-      <c r="C3" s="2" t="inlineStr">
+    <row r="11" ht="196.5" customHeight="1">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>task_tables_relation_row_compare_label</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>lower_of_two_rows</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Use the table values to decide which named row wins the comparison. Look at the Score column for rows Saba and Darb. Which row is smaller?
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Find which of the two specified rows has the requested value relation in the named column. Between rows Lula and Eng, which has the lower value in the Score column?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
+Answer format: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Milo"}</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Find which of the two specified rows has the requested value relation in the named column. Between rows Lula and Eng, which has the lower value in the Score column?
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"answer":"Milo"}</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[406.464, 499.333, 526.848, 588.0], [406.464, 233.333, 526.848, 322.0]], "answer": "Lula"}</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>[[406.464, 499.333, 526.848, 588.0], [406.464, 233.333, 526.848, 322.0]]</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>2481226809019608</v>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/images/lower_of_two_rows/0018.png</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/data/lower_of_two_rows/0018.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="196.5" customHeight="1">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_relation_row_compare_label</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>lower_of_two_rows</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Work from the styled table shown in the image: a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Read the table and report which named row satisfies the requested comparison. Compare the Pts entries for rows Raab and Cate. Which row has the lower value?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence format: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
 Answer requirement: set "answer" to the row label with the requested higher or lower value.
@@ -4798,63 +5374,127 @@
 {"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Milo"}</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Use the table values to decide which named row wins the comparison. Look at the Score column for rows Saba and Darb. Which row is smaller?
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Work from the styled table shown in the image: a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Read the table and report which named row satisfies the requested comparison. Compare the Pts entries for rows Raab and Cate. Which row has the lower value?
 Return a valid JSON object with key "answer".
 Answer requirement: set "answer" to the row label with the requested higher or lower value.
 Example JSON:
 {"answer":"Milo"}</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[737.52, 528.889, 888.0, 588.0], [737.52, 292.444, 888.0, 351.556]], "answer": "Darb"}</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>[[737.52, 528.889, 888.0, 588.0], [737.52, 292.444, 888.0, 351.556]]</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[687.36, 360.0, 888.0, 436.0], [687.36, 512.0, 888.0, 588.0]], "answer": "Cate"}</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>[[687.36, 360.0, 888.0, 436.0], [687.36, 512.0, 888.0, 588.0]]</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K3" t="n">
-        <v>295710198618759</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/images/lower_of_two_rows/0001.png</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/data/lower_of_two_rows/0001.json</t>
+      <c r="K12" t="n">
+        <v>2726924123429784</v>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/images/lower_of_two_rows/0003.png</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/data/lower_of_two_rows/0003.json</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="196.5" customHeight="1">
-      <c r="C4" s="2" t="inlineStr">
+    <row r="13" ht="196.5" customHeight="1">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>task_tables_relation_row_compare_label</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>lower_of_two_rows</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Use the table values to decide which named row wins the comparison. Between rows Jeff and Jody, which has the lower value in the Gain column?
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Work from the styled table shown in the image: a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Find which of the two specified rows has the requested value relation in the named column. Which row, Caye or Mera, has the smaller value in the Mass column?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
+Answer: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Milo"}</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Work from the styled table shown in the image: a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Find which of the two specified rows has the requested value relation in the named column. Which row, Caye or Mera, has the smaller value in the Mass column?
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"answer":"Milo"}</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[286.08, 322.0, 486.72, 410.667], [286.08, 144.667, 486.72, 233.333]], "answer": "Mera"}</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>[[286.08, 322.0, 486.72, 410.667], [286.08, 144.667, 486.72, 233.333]]</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>2946372987182229</v>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/images/lower_of_two_rows/0009.png</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/data/lower_of_two_rows/0009.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="196.5" customHeight="1">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_relation_row_compare_label</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>lower_of_two_rows</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Read the table and report which named row satisfies the requested comparison. Compare the Pts entries for rows Haag and Jesh. Which row has the lower value?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence rule: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
 Answer rule: set "answer" to the row label with the requested higher or lower value.
@@ -4862,63 +5502,63 @@
 {"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Milo"}</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Use the table values to decide which named row wins the comparison. Between rows Jeff and Jody, which has the lower value in the Gain column?
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Read the table and report which named row satisfies the requested comparison. Compare the Pts entries for rows Haag and Jesh. Which row has the lower value?
 Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the row label with the requested higher or lower value.
+Answer: set "answer" to the row label with the requested higher or lower value.
 Example JSON:
 {"answer":"Milo"}</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[587.04, 208.0, 737.52, 284.0], [587.04, 360.0, 737.52, 436.0]], "answer": "Jody"}</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>[[587.04, 208.0, 737.52, 284.0], [587.04, 360.0, 737.52, 436.0]]</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[587.04, 132.0, 737.52, 208.0], [587.04, 284.0, 737.52, 360.0]], "answer": "Jesh"}</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>[[587.04, 132.0, 737.52, 208.0], [587.04, 284.0, 737.52, 360.0]]</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K4" t="n">
-        <v>1013422073186745</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/images/lower_of_two_rows/0009.png</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/data/lower_of_two_rows/0009.json</t>
+      <c r="K14" t="n">
+        <v>3344029651290864</v>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/images/lower_of_two_rows/0000.png</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/data/lower_of_two_rows/0000.json</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="196.5" customHeight="1">
-      <c r="C5" s="2" t="inlineStr">
+    <row r="15" ht="196.5" customHeight="1">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>task_tables_relation_row_compare_label</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>lower_of_two_rows</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Use the table values to decide which named row wins the comparison. Look at the Gain column for rows Kyle and Zurn. Which row is smaller?
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Use the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Answer this question. Look at the Mass column for rows Oby and Oren. Which row is smaller?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence requirement: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
 Answer format: set "answer" to the row label with the requested higher or lower value.
@@ -4926,63 +5566,63 @@
 {"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Milo"}</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Use the table values to decide which named row wins the comparison. Look at the Gain column for rows Kyle and Zurn. Which row is smaller?
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Use the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Answer this question. Look at the Mass column for rows Oby and Oren. Which row is smaller?
 Return a valid JSON object with key "answer".
-Answer: set "answer" to the row label with the requested higher or lower value.
+Answer format: set "answer" to the row label with the requested higher or lower value.
 Example JSON:
 {"answer":"Milo"}</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[687.36, 297.818, 888.0, 346.182], [687.36, 491.273, 888.0, 539.636]], "answer": "Zurn"}</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>[[687.36, 297.818, 888.0, 346.182], [687.36, 491.273, 888.0, 539.636]]</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[286.08, 322.0, 436.56, 388.5], [286.08, 255.5, 436.56, 322.0]], "answer": "Oren"}</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>[[286.08, 322.0, 436.56, 388.5], [286.08, 255.5, 436.56, 322.0]]</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K5" t="n">
-        <v>1062335918501079</v>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/images/lower_of_two_rows/0011.png</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/data/lower_of_two_rows/0011.json</t>
+      <c r="K15" t="n">
+        <v>3577358525879256</v>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/images/lower_of_two_rows/0023.png</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/data/lower_of_two_rows/0023.json</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="196.5" customHeight="1">
-      <c r="C6" s="2" t="inlineStr">
+    <row r="16" ht="196.5" customHeight="1">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>task_tables_relation_row_compare_label</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>lower_of_two_rows</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Compare the two named rows in the requested numeric column. Between rows Chi and Pugh, which has the lower value in the Temp column?
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Use the table values to decide which named row wins the comparison. Compare the Cost entries for rows Os and Esma. Which row has the lower value?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence requirement: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
 Answer format: set "answer" to the row label with the requested higher or lower value.
@@ -4990,63 +5630,511 @@
 {"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Milo"}</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Compare the two named rows in the requested numeric column. Between rows Chi and Pugh, which has the lower value in the Temp column?
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Use the table values to decide which named row wins the comparison. Compare the Cost entries for rows Os and Esma. Which row has the lower value?
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"answer":"Milo"}</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[486.72, 351.556, 687.36, 410.667], [486.72, 115.111, 687.36, 174.222]], "answer": "Os"}</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>[[486.72, 351.556, 687.36, 410.667], [486.72, 115.111, 687.36, 174.222]]</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>3611186241149129</v>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/images/lower_of_two_rows/0013.png</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/data/lower_of_two_rows/0013.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="196.5" customHeight="1">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_relation_row_compare_label</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>lower_of_two_rows</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Work from the styled table shown in the image: a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Answer this question. Between rows Huai and Adey, which has the lower value in the Score column?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
+Answer rule: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Milo"}</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Work from the styled table shown in the image: a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Answer this question. Between rows Huai and Adey, which has the lower value in the Score column?
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"answer":"Milo"}</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[587.04, 539.636, 737.52, 588.0], [587.04, 394.545, 737.52, 442.909]], "answer": "Adey"}</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>[[587.04, 539.636, 737.52, 588.0], [587.04, 394.545, 737.52, 442.909]]</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>4467069646870284</v>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/images/lower_of_two_rows/0010.png</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/data/lower_of_two_rows/0010.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="196.5" customHeight="1">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_relation_row_compare_label</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>lower_of_two_rows</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Use the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Answer this question. In the Rank column, which row is smaller: Egin or Voss?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
+Answer requirement: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Milo"}</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Use the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Answer this question. In the Rank column, which row is smaller: Egin or Voss?
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"answer":"Milo"}</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[406.464, 144.667, 526.848, 233.333], [406.464, 322.0, 526.848, 410.667]], "answer": "Voss"}</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>[[406.464, 144.667, 526.848, 233.333], [406.464, 322.0, 526.848, 410.667]]</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>5195950928412901</v>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/images/lower_of_two_rows/0001.png</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/data/lower_of_two_rows/0001.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="196.5" customHeight="1">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_relation_row_compare_label</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>lower_of_two_rows</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Use the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Read the table and report which named row satisfies the requested comparison. Compare the Time entries for rows Miru and Brod. Which row has the lower value?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
+Answer format: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Milo"}</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Use the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Read the table and report which named row satisfies the requested comparison. Compare the Time entries for rows Miru and Brod. Which row has the lower value?
 Return a valid JSON object with key "answer".
 Answer: set "answer" to the row label with the requested higher or lower value.
 Example JSON:
 {"answer":"Milo"}</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[737.52, 201.091, 888.0, 249.455], [737.52, 152.727, 888.0, 201.091]], "answer": "Chi"}</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>[[737.52, 201.091, 888.0, 249.455], [737.52, 152.727, 888.0, 201.091]]</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[647.232, 375.2, 767.616, 428.4], [647.232, 109.2, 767.616, 162.4]], "answer": "Miru"}</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>[[647.232, 375.2, 767.616, 428.4], [647.232, 109.2, 767.616, 162.4]]</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K6" t="n">
-        <v>1078380476589662</v>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/images/lower_of_two_rows/0010.png</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/data/lower_of_two_rows/0010.json</t>
+      <c r="K19" t="n">
+        <v>5313751226388122</v>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/images/lower_of_two_rows/0012.png</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/data/lower_of_two_rows/0012.json</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="196.5" customHeight="1">
-      <c r="C7" s="2" t="inlineStr">
+    <row r="20" ht="196.5" customHeight="1">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>task_tables_relation_row_compare_label</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>lower_of_two_rows</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Answer this question. Look at the Pts column for rows Tina and Ivy. Which row is smaller?
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Use the table in the image. It shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Read the table and report which named row satisfies the requested comparison. Between rows Sum and Chlo, which has the lower value in the Rank column?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
+Answer format: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Milo"}</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Use the table in the image. It shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Read the table and report which named row satisfies the requested comparison. Between rows Sum and Chlo, which has the lower value in the Rank column?
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"answer":"Milo"}</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[286.08, 322.0, 436.56, 410.667], [286.08, 233.333, 436.56, 322.0]], "answer": "Sum"}</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>[[286.08, 322.0, 436.56, 410.667], [286.08, 233.333, 436.56, 322.0]]</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>6460928801623225</v>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/images/lower_of_two_rows/0004.png</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/data/lower_of_two_rows/0004.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="196.5" customHeight="1">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_relation_row_compare_label</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>lower_of_two_rows</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Use the table in the image. It shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Read the table and report which named row satisfies the requested comparison. Compare the Rate entries for rows Allx and Frey. Which row has the lower value?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
+Answer rule: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Milo"}</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Use the table in the image. It shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Read the table and report which named row satisfies the requested comparison. Compare the Rate entries for rows Allx and Frey. Which row has the lower value?
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"answer":"Milo"}</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[587.04, 109.2, 737.52, 162.4], [587.04, 268.8, 737.52, 322.0]], "answer": "Frey"}</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>[[587.04, 109.2, 737.52, 162.4], [587.04, 268.8, 737.52, 322.0]]</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>6580159525872604</v>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/images/lower_of_two_rows/0005.png</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/data/lower_of_two_rows/0005.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="196.5" customHeight="1">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_relation_row_compare_label</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>lower_of_two_rows</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Compare the two named rows in the requested numeric column. Compare the Mass entries for rows Serg and Hare. Which row has the lower value?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
+Answer requirement: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Milo"}</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Compare the two named rows in the requested numeric column. Compare the Mass entries for rows Serg and Hare. Which row has the lower value?
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"answer":"Milo"}</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[406.464, 436.0, 526.848, 512.0], [406.464, 512.0, 526.848, 588.0]], "answer": "Hare"}</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>[[406.464, 436.0, 526.848, 512.0], [406.464, 512.0, 526.848, 588.0]]</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>6795803487266181</v>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/images/lower_of_two_rows/0017.png</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/data/lower_of_two_rows/0017.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="196.5" customHeight="1">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_relation_row_compare_label</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>lower_of_two_rows</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Work from the styled table shown in the image: a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Read the table and report which named row satisfies the requested comparison. Between rows Nett and Nika, which has the lower value in the Age column?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
+Answer requirement: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Milo"}</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Work from the styled table shown in the image: a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Read the table and report which named row satisfies the requested comparison. Between rows Nett and Nika, which has the lower value in the Age column?
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the row label with the requested higher or lower value.
+Example JSON:
+{"answer":"Milo"}</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[286.08, 499.333, 406.464, 588.0], [286.08, 144.667, 406.464, 233.333]], "answer": "Nett"}</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>[[286.08, 499.333, 406.464, 588.0], [286.08, 144.667, 406.464, 233.333]]</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>6841442769452837</v>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/images/lower_of_two_rows/0015.png</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/data/lower_of_two_rows/0015.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="196.5" customHeight="1">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_relation_row_compare_label</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>lower_of_two_rows</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Work from the styled table shown in the image: a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Find which of the two specified rows has the requested value relation in the named column. Compare the Pts entries for rows Eri and Jone. Which row has the lower value?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
 Answer: set "answer" to the row label with the requested higher or lower value.
@@ -5054,319 +6142,63 @@
 {"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Milo"}</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Answer this question. Look at the Pts column for rows Tina and Ivy. Which row is smaller?
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Work from the styled table shown in the image: a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Find which of the two specified rows has the requested value relation in the named column. Compare the Pts entries for rows Eri and Jone. Which row has the lower value?
 Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the row label with the requested higher or lower value.
+Answer: set "answer" to the row label with the requested higher or lower value.
 Example JSON:
 {"answer":"Milo"}</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[767.616, 284.0, 888.0, 360.0], [767.616, 436.0, 888.0, 512.0]], "answer": "Ivy"}</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>[[767.616, 284.0, 888.0, 360.0], [767.616, 436.0, 888.0, 512.0]]</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[486.72, 115.111, 687.36, 174.222], [486.72, 174.222, 687.36, 233.333]], "answer": "Jone"}</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>[[486.72, 115.111, 687.36, 174.222], [486.72, 174.222, 687.36, 233.333]]</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K7" t="n">
-        <v>1654339631390634</v>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/images/lower_of_two_rows/0019.png</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/data/lower_of_two_rows/0019.json</t>
+      <c r="K24" t="n">
+        <v>7189242083001268</v>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/images/lower_of_two_rows/0007.png</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/data/lower_of_two_rows/0007.json</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="196.5" customHeight="1">
-      <c r="C8" s="2" t="inlineStr">
+    <row r="25" ht="196.5" customHeight="1">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>task_tables_relation_row_compare_label</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>lower_of_two_rows</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Work from the styled table shown in the image: a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Use the table values to decide which named row wins the comparison. In the Cost column, which row is smaller: Nedi or Eoin?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
-Answer format: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Milo"}</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Work from the styled table shown in the image: a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Use the table values to decide which named row wins the comparison. In the Cost column, which row is smaller: Nedi or Eoin?
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"answer":"Milo"}</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[436.56, 292.444, 587.04, 351.556], [436.56, 528.889, 587.04, 588.0]], "answer": "Nedi"}</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>[[436.56, 292.444, 587.04, 351.556], [436.56, 528.889, 587.04, 588.0]]</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>1655293385989196</v>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/images/lower_of_two_rows/0008.png</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/data/lower_of_two_rows/0008.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="196.5" customHeight="1">
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>lower_of_two_rows</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Compare the two named rows in the requested numeric column. Compare the Score entries for rows Ling and Chun. Which row has the lower value?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
-Answer format: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Milo"}</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Compare the two named rows in the requested numeric column. Compare the Score entries for rows Ling and Chun. Which row has the lower value?
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"answer":"Milo"}</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[687.36, 322.0, 888.0, 410.667], [687.36, 144.667, 888.0, 233.333]], "answer": "Ling"}</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>[[687.36, 322.0, 888.0, 410.667], [687.36, 144.667, 888.0, 233.333]]</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>3007511573478354</v>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/images/lower_of_two_rows/0021.png</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/data/lower_of_two_rows/0021.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="196.5" customHeight="1">
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>lower_of_two_rows</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>You are given a table: a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Read the table and report which named row satisfies the requested comparison. Compare the Temp entries for rows Eve and Coco. Which row has the lower value?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
-Answer format: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Milo"}</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>You are given a table: a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Read the table and report which named row satisfies the requested comparison. Compare the Temp entries for rows Eve and Coco. Which row has the lower value?
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"answer":"Milo"}</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[767.616, 233.333, 888.0, 322.0], [767.616, 322.0, 888.0, 410.667]], "answer": "Coco"}</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>[[767.616, 233.333, 888.0, 322.0], [767.616, 322.0, 888.0, 410.667]]</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>3090721071669862</v>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/images/lower_of_two_rows/0018.png</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/data/lower_of_two_rows/0018.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="196.5" customHeight="1">
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>lower_of_two_rows</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Use the table values to decide which named row wins the comparison. Compare the Time entries for rows Ful and Ver. Which row has the lower value?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
-Answer format: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Milo"}</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Use the table values to decide which named row wins the comparison. Compare the Time entries for rows Ful and Ver. Which row has the lower value?
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"answer":"Milo"}</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[767.616, 375.2, 888.0, 428.4], [767.616, 481.6, 888.0, 534.8]], "answer": "Ver"}</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>[[767.616, 375.2, 888.0, 428.4], [767.616, 481.6, 888.0, 534.8]]</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>3195433717440934</v>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/images/lower_of_two_rows/0012.png</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/data/lower_of_two_rows/0012.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="196.5" customHeight="1">
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>lower_of_two_rows</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Compare the two named rows in the requested numeric column. Between rows Nina and Rosa, which has the lower value in the Wins column?
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Find which of the two specified rows has the requested value relation in the named column. Look at the Cost column for rows Chon and Lat. Which row is smaller?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
 Answer: set "answer" to the row label with the requested higher or lower value.
@@ -5374,127 +6206,63 @@
 {"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Milo"}</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Compare the two named rows in the requested numeric column. Between rows Nina and Rosa, which has the lower value in the Wins column?
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"answer":"Milo"}</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[587.04, 539.636, 737.52, 588.0], [587.04, 442.909, 737.52, 491.273]], "answer": "Nina"}</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>[[587.04, 539.636, 737.52, 588.0], [587.04, 442.909, 737.52, 491.273]]</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>3237468293657804</v>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/images/lower_of_two_rows/0022.png</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/data/lower_of_two_rows/0022.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="196.5" customHeight="1">
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>lower_of_two_rows</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Read the table and report which named row satisfies the requested comparison. Which row, Ogg or Aryn, has the smaller value in the Rank column?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
-Answer rule: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Milo"}</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Read the table and report which named row satisfies the requested comparison. Which row, Ogg or Aryn, has the smaller value in the Rank column?
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Find which of the two specified rows has the requested value relation in the named column. Look at the Cost column for rows Chon and Lat. Which row is smaller?
 Return a valid JSON object with key "answer".
 Answer field: set "answer" to the row label with the requested higher or lower value.
 Example JSON:
 {"answer":"Milo"}</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[486.72, 512.0, 687.36, 588.0], [486.72, 284.0, 687.36, 360.0]], "answer": "Ogg"}</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>[[486.72, 512.0, 687.36, 588.0], [486.72, 284.0, 687.36, 360.0]]</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[737.52, 410.667, 888.0, 499.333], [737.52, 499.333, 888.0, 588.0]], "answer": "Lat"}</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>[[737.52, 410.667, 888.0, 499.333], [737.52, 499.333, 888.0, 588.0]]</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K13" t="n">
-        <v>3430447221003943</v>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/images/lower_of_two_rows/0014.png</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/data/lower_of_two_rows/0014.json</t>
+      <c r="K25" t="n">
+        <v>8127468273214046</v>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/images/lower_of_two_rows/0008.png</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_relation_row_compare_label/data/lower_of_two_rows/0008.json</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="196.5" customHeight="1">
-      <c r="C14" s="2" t="inlineStr">
+    <row r="26" ht="196.5" customHeight="1">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>task_tables_relation_row_compare_label</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>lower_of_two_rows</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Answer this question. In the Temp column, which row is smaller: Erb or Ilka?
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Answer this question. Which row, Resa or Pump, has the smaller value in the Dist column?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence field: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
 Answer field: set "answer" to the row label with the requested higher or lower value.
@@ -5502,814 +6270,46 @@
 {"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Milo"}</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Answer this question. In the Temp column, which row is smaller: Erb or Ilka?
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"answer":"Milo"}</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[647.232, 512.0, 767.616, 588.0], [647.232, 208.0, 767.616, 284.0]], "answer": "Erb"}</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>[[647.232, 512.0, 767.616, 588.0], [647.232, 208.0, 767.616, 284.0]]</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>3634208655971262</v>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/images/lower_of_two_rows/0005.png</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/data/lower_of_two_rows/0005.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="196.5" customHeight="1">
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>lower_of_two_rows</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Find which of the two specified rows has the requested value relation in the named column. Which row, Tham or Kyd, has the smaller value in the Temp column?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
-Answer rule: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Milo"}</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Find which of the two specified rows has the requested value relation in the named column. Which row, Tham or Kyd, has the smaller value in the Temp column?
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"answer":"Milo"}</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[737.52, 455.0, 888.0, 521.5], [737.52, 122.5, 888.0, 189.0]], "answer": "Tham"}</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>[[737.52, 455.0, 888.0, 521.5], [737.52, 122.5, 888.0, 189.0]]</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>4000324952346714</v>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/images/lower_of_two_rows/0023.png</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/data/lower_of_two_rows/0023.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="196.5" customHeight="1">
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>lower_of_two_rows</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Answer this question. Compare the Time entries for rows Peti and Mika. Which row has the lower value?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
-Answer rule: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Milo"}</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Answer this question. Compare the Time entries for rows Peti and Mika. Which row has the lower value?
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"answer":"Milo"}</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[286.08, 249.455, 436.56, 297.818], [286.08, 491.273, 436.56, 539.636]], "answer": "Mika"}</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>[[286.08, 249.455, 436.56, 297.818], [286.08, 491.273, 436.56, 539.636]]</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>5030209001075089</v>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/images/lower_of_two_rows/0003.png</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/data/lower_of_two_rows/0003.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="196.5" customHeight="1">
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>lower_of_two_rows</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Answer this question. Which row, Chic or Wit, has the smaller value in the Time column?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
-Answer rule: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Milo"}</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Answer this question. Which row, Chic or Wit, has the smaller value in the Time column?
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"answer":"Milo"}</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[286.08, 410.667, 406.464, 469.778], [286.08, 528.889, 406.464, 588.0]], "answer": "Wit"}</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>[[286.08, 410.667, 406.464, 469.778], [286.08, 528.889, 406.464, 588.0]]</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>5057991729399364</v>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/images/lower_of_two_rows/0000.png</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/data/lower_of_two_rows/0000.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="196.5" customHeight="1">
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>lower_of_two_rows</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>You are given a table: a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Use the table values to decide which named row wins the comparison. Look at the Rate column for rows Hebe and Herv. Which row is smaller?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
-Answer field: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Milo"}</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>You are given a table: a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Use the table values to decide which named row wins the comparison. Look at the Rate column for rows Hebe and Herv. Which row is smaller?
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"answer":"Milo"}</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[436.56, 521.5, 587.04, 588.0], [436.56, 255.5, 587.04, 322.0]], "answer": "Hebe"}</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>[[436.56, 521.5, 587.04, 588.0], [436.56, 255.5, 587.04, 322.0]]</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>5202847224579150</v>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/images/lower_of_two_rows/0007.png</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/data/lower_of_two_rows/0007.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="196.5" customHeight="1">
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>lower_of_two_rows</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Compare the two named rows in the requested numeric column. Between rows Aba and Foss, which has the lower value in the Mass column?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
-Answer requirement: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Milo"}</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Compare the two named rows in the requested numeric column. Between rows Aba and Foss, which has the lower value in the Mass column?
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"answer":"Milo"}</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[687.36, 174.222, 888.0, 233.333], [687.36, 528.889, 888.0, 588.0]], "answer": "Aba"}</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>[[687.36, 174.222, 888.0, 233.333], [687.36, 528.889, 888.0, 588.0]]</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>5465230830114286</v>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/images/lower_of_two_rows/0020.png</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/data/lower_of_two_rows/0020.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="196.5" customHeight="1">
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>lower_of_two_rows</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Answer this question. Between rows Farr and Axel, which has the lower value in the Score column?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
-Answer rule: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Milo"}</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Answer this question. Between rows Farr and Axel, which has the lower value in the Score column?
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"answer":"Milo"}</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[436.56, 375.2, 587.04, 428.4], [436.56, 322.0, 587.04, 375.2]], "answer": "Axel"}</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>[[436.56, 375.2, 587.04, 428.4], [436.56, 322.0, 587.04, 375.2]]</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>5474079393045528</v>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/images/lower_of_two_rows/0004.png</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/data/lower_of_two_rows/0004.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="196.5" customHeight="1">
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>lower_of_two_rows</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Use the table values to decide which named row wins the comparison. Between rows Karp and Flem, which has the lower value in the Rank column?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
-Answer requirement: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Milo"}</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Use the table values to decide which named row wins the comparison. Between rows Karp and Flem, which has the lower value in the Rank column?
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Answer this question. Which row, Resa or Pump, has the smaller value in the Dist column?
 Return a valid JSON object with key "answer".
 Answer field: set "answer" to the row label with the requested higher or lower value.
 Example JSON:
 {"answer":"Milo"}</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[767.616, 284.0, 888.0, 360.0], [767.616, 436.0, 888.0, 512.0]], "answer": "Flem"}</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>[[767.616, 284.0, 888.0, 360.0], [767.616, 436.0, 888.0, 512.0]]</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[687.36, 297.818, 888.0, 346.182], [687.36, 539.636, 888.0, 588.0]], "answer": "Pump"}</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>[[687.36, 297.818, 888.0, 346.182], [687.36, 539.636, 888.0, 588.0]]</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K21" t="n">
-        <v>5562011015227954</v>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/images/lower_of_two_rows/0006.png</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/data/lower_of_two_rows/0006.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="196.5" customHeight="1">
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>lower_of_two_rows</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Read the table and report which named row satisfies the requested comparison. Compare the Rate entries for rows Si and Leon. Which row has the lower value?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
-Answer format: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Milo"}</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Read the table and report which named row satisfies the requested comparison. Compare the Rate entries for rows Si and Leon. Which row has the lower value?
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"answer":"Milo"}</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[286.08, 255.5, 486.72, 322.0], [286.08, 122.5, 486.72, 189.0]], "answer": "Si"}</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>[[286.08, 255.5, 486.72, 322.0], [286.08, 122.5, 486.72, 189.0]]</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>6347938236947639</v>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/images/lower_of_two_rows/0024.png</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/data/lower_of_two_rows/0024.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="196.5" customHeight="1">
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>lower_of_two_rows</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Compare the two named rows in the requested numeric column. Which row, Phyl or Hew, has the smaller value in the Rate column?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
-Answer: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Milo"}</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Compare the two named rows in the requested numeric column. Which row, Phyl or Hew, has the smaller value in the Rate column?
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"answer":"Milo"}</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[486.72, 122.5, 687.36, 189.0], [486.72, 255.5, 687.36, 322.0]], "answer": "Hew"}</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>[[486.72, 122.5, 687.36, 189.0], [486.72, 255.5, 687.36, 322.0]]</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K23" t="n">
-        <v>6769239774417096</v>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/images/lower_of_two_rows/0002.png</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/data/lower_of_two_rows/0002.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="196.5" customHeight="1">
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>lower_of_two_rows</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Use the table values to decide which named row wins the comparison. Look at the Rank column for rows Ute and Drue. Which row is smaller?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
-Answer rule: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Milo"}</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Use the table values to decide which named row wins the comparison. Look at the Rank column for rows Ute and Drue. Which row is smaller?
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"answer":"Milo"}</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[406.464, 255.5, 526.848, 322.0], [406.464, 388.5, 526.848, 455.0]], "answer": "Drue"}</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>[[406.464, 255.5, 526.848, 322.0], [406.464, 388.5, 526.848, 455.0]]</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K24" t="n">
-        <v>6977918049150490</v>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/images/lower_of_two_rows/0015.png</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/data/lower_of_two_rows/0015.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="196.5" customHeight="1">
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>lower_of_two_rows</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Work from the styled table shown in the image: a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Read the table and report which named row satisfies the requested comparison. Compare the Mass entries for rows Gitt and Mini. Which row has the lower value?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
-Answer field: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Milo"}</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Work from the styled table shown in the image: a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Read the table and report which named row satisfies the requested comparison. Compare the Mass entries for rows Gitt and Mini. Which row has the lower value?
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"answer":"Milo"}</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[286.08, 297.818, 406.464, 346.182], [286.08, 249.455, 406.464, 297.818]], "answer": "Mini"}</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>[[286.08, 297.818, 406.464, 346.182], [286.08, 249.455, 406.464, 297.818]]</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K25" t="n">
-        <v>7007668729282998</v>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/images/lower_of_two_rows/0017.png</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label/data/lower_of_two_rows/0017.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="196.5" customHeight="1">
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_relation_row_compare_label</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>lower_of_two_rows</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Find which of the two specified rows has the requested value relation in the named column. Between rows Dyl and Jaco, which has the lower value in the Gain column?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two compared value cells in the prompt.
-Answer: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"evidence":[[260,180,372,236],[260,238,372,294]],"answer":"Milo"}</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Find which of the two specified rows has the requested value relation in the named column. Between rows Dyl and Jaco, which has the lower value in the Gain column?
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the row label with the requested higher or lower value.
-Example JSON:
-{"answer":"Milo"}</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[647.232, 351.556, 767.616, 410.667], [647.232, 292.444, 767.616, 351.556]], "answer": "Jaco"}</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>[[647.232, 351.556, 767.616, 410.667], [647.232, 292.444, 767.616, 351.556]]</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
       <c r="K26" t="n">
-        <v>7185545759933616</v>
+        <v>8748795934678401</v>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>task_tables_relation_row_compare_label/images/lower_of_two_rows/0016.png</t>
+          <t>tables/task_tables_relation_row_compare_label/images/lower_of_two_rows/0021.png</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>task_tables_relation_row_compare_label/data/lower_of_two_rows/0016.json</t>
+          <t>tables/task_tables_relation_row_compare_label/data/lower_of_two_rows/0021.json</t>
         </is>
       </c>
     </row>
